--- a/Documents/ユースケース記述new_山形.xlsx
+++ b/Documents/ユースケース記述new_山形.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB6B953-011C-420C-9D53-83B8D1CD9095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37587A59-9FB5-4C0D-B604-DE2C691BDCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,23 +310,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>①メニュー画面でログアウトボタンを押下する
-②ログイン画面へ遷移する</t>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ログイン画面が表示される</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -364,6 +347,24 @@
       <t>ガメン</t>
     </rPh>
     <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①メニュー画面でログアウトボタンを押下する
+②ログアウト画面が表示される
+③ログイン画面へ遷移する</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -1257,36 +1258,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1311,14 +1282,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1332,49 +1345,40 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1398,17 +1402,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1416,23 +1417,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2824,19 +2825,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -2848,72 +2849,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
+      <c r="A2" s="49"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="78" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="57"/>
+      <c r="F2" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="104">
+      <c r="G2" s="57"/>
+      <c r="H2" s="60">
         <v>45805</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="70"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="75" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="81" t="s">
         <v>68</v>
       </c>
       <c r="E6" s="39"/>
@@ -2921,15 +2922,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="75" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="81" t="s">
         <v>76</v>
       </c>
       <c r="E7" s="39"/>
@@ -2937,63 +2938,63 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="75" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
-        <v>81</v>
+      <c r="D8" s="81" t="s">
+        <v>80</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="74" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="103" t="s">
-        <v>80</v>
+      <c r="D9" s="83" t="s">
+        <v>79</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="82"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="70" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="74" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="52"/>
+      <c r="D10" s="81"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="J10" s="82"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="69"/>
-      <c r="B11" s="70" t="s">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="103" t="s">
+      <c r="D11" s="83" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="39"/>
@@ -3001,54 +3002,54 @@
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="82"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="75" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="52" t="s">
-        <v>79</v>
+      <c r="D12" s="81" t="s">
+        <v>78</v>
       </c>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="82"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1" thickBot="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="77" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="65"/>
-      <c r="F16" s="77" t="s">
+      <c r="E16" s="55"/>
+      <c r="F16" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="65"/>
+      <c r="G16" s="55"/>
       <c r="H16" s="5" t="s">
         <v>8</v>
       </c>
@@ -3060,72 +3061,72 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="59"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="78" t="s">
+      <c r="C17" s="50"/>
+      <c r="D17" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="79"/>
-      <c r="F17" s="78" t="s">
+      <c r="E17" s="57"/>
+      <c r="F17" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="79"/>
-      <c r="H17" s="104">
+      <c r="G17" s="57"/>
+      <c r="H17" s="60">
         <v>45805</v>
       </c>
-      <c r="I17" s="71" t="s">
+      <c r="I17" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="J17" s="74"/>
+      <c r="J17" s="64"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="59"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="75"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="65"/>
     </row>
     <row r="19" spans="1:10" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A19" s="61"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="76"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="49" t="s">
+      <c r="B20" s="68"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="51"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="70"/>
     </row>
     <row r="21" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="75" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="81" t="s">
         <v>74</v>
       </c>
       <c r="E21" s="39"/>
@@ -3133,15 +3134,15 @@
       <c r="G21" s="39"/>
       <c r="H21" s="39"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="82"/>
     </row>
     <row r="22" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="75" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="81" t="s">
         <v>76</v>
       </c>
       <c r="E22" s="39"/>
@@ -3149,15 +3150,15 @@
       <c r="G22" s="39"/>
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="82"/>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="75" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="81" t="s">
         <v>75</v>
       </c>
       <c r="E23" s="39"/>
@@ -3165,83 +3166,83 @@
       <c r="G23" s="39"/>
       <c r="H23" s="39"/>
       <c r="I23" s="39"/>
-      <c r="J23" s="53"/>
+      <c r="J23" s="82"/>
     </row>
     <row r="24" spans="1:10" ht="60" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="74" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="40"/>
-      <c r="D24" s="103" t="s">
-        <v>77</v>
+      <c r="D24" s="83" t="s">
+        <v>81</v>
       </c>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
-      <c r="J24" s="53"/>
+      <c r="J24" s="82"/>
     </row>
     <row r="25" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A25" s="68"/>
-      <c r="B25" s="70" t="s">
+      <c r="A25" s="72"/>
+      <c r="B25" s="74" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="40"/>
-      <c r="D25" s="52"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
-      <c r="J25" s="53"/>
+      <c r="J25" s="82"/>
     </row>
     <row r="26" spans="1:10" ht="60" customHeight="1">
-      <c r="A26" s="69"/>
-      <c r="B26" s="70" t="s">
+      <c r="A26" s="73"/>
+      <c r="B26" s="74" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="40"/>
-      <c r="D26" s="103"/>
+      <c r="D26" s="83"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="39"/>
       <c r="H26" s="39"/>
       <c r="I26" s="39"/>
-      <c r="J26" s="53"/>
+      <c r="J26" s="82"/>
     </row>
     <row r="27" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="75" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="52" t="s">
-        <v>78</v>
+      <c r="D27" s="81" t="s">
+        <v>77</v>
       </c>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="39"/>
       <c r="H27" s="39"/>
       <c r="I27" s="39"/>
-      <c r="J27" s="53"/>
+      <c r="J27" s="82"/>
     </row>
     <row r="28" spans="1:10" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="48"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="80"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4217,31 +4218,19 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A16:C19"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E19"/>
-    <mergeCell ref="F17:G19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:J20"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D21:J21"/>
     <mergeCell ref="D1:E1"/>
@@ -4258,19 +4247,31 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="A16:C19"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E19"/>
+    <mergeCell ref="F17:G19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4289,19 +4290,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4313,40 +4314,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
+      <c r="A2" s="49"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="74"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5702,19 +5703,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5726,40 +5727,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
+      <c r="A2" s="49"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="74"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7109,19 +7110,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7133,54 +7134,54 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
+      <c r="A2" s="49"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="74"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="65"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="70"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="85" t="s">
@@ -7194,22 +7195,22 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="89"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="90"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7218,10 +7219,10 @@
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
-      <c r="J8" s="90"/>
+      <c r="J8" s="91"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7230,10 +7231,10 @@
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="42"/>
-      <c r="J9" s="90"/>
+      <c r="J9" s="91"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7242,10 +7243,10 @@
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="42"/>
-      <c r="J10" s="90"/>
+      <c r="J10" s="91"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7254,10 +7255,10 @@
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
-      <c r="J11" s="90"/>
+      <c r="J11" s="91"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7266,10 +7267,10 @@
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
-      <c r="J12" s="90"/>
+      <c r="J12" s="91"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="59"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7278,7 +7279,7 @@
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
       <c r="I13" s="42"/>
-      <c r="J13" s="90"/>
+      <c r="J13" s="91"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="85" t="s">
@@ -7292,7 +7293,7 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="82"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="85" t="s">
@@ -7300,7 +7301,7 @@
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="52"/>
+      <c r="D15" s="81"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
@@ -7328,95 +7329,95 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="91" t="s">
+      <c r="H16" s="92" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="53"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="84"/>
+      <c r="A17" s="86"/>
       <c r="B17" s="39"/>
       <c r="C17" s="40"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="52"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="82"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="84"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="39"/>
       <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="52"/>
+      <c r="H18" s="81"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="53"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="84"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="39"/>
       <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="52"/>
+      <c r="H19" s="81"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="53"/>
+      <c r="J19" s="82"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="84"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="52"/>
+      <c r="H20" s="81"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="53"/>
+      <c r="J20" s="82"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="84"/>
+      <c r="A21" s="86"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="52"/>
+      <c r="H21" s="81"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="82"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="84"/>
+      <c r="A22" s="86"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
+      <c r="H22" s="81"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="82"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="83"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="55"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="48"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8397,11 +8398,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
@@ -8411,23 +8423,12 @@
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8446,130 +8447,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="77" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="77" t="s">
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="77" t="s">
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="77" t="s">
+      <c r="P1" s="55"/>
+      <c r="Q1" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="65"/>
-      <c r="S1" s="77" t="s">
+      <c r="R1" s="55"/>
+      <c r="S1" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="51"/>
+      <c r="T1" s="70"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
+      <c r="A2" s="49"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="89"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="90"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="80"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="58"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="80"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="90"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="91"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="101"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="49" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="51"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="70"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="85" t="s">
@@ -8580,7 +8581,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="81" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -8595,7 +8596,7 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="53"/>
+      <c r="T6" s="82"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="85" t="s">
@@ -8606,7 +8607,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="81" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="39"/>
@@ -8621,7 +8622,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="53"/>
+      <c r="T7" s="82"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8824,29 +8825,29 @@
         <v>46</v>
       </c>
       <c r="B15" s="40"/>
-      <c r="C15" s="100" t="s">
+      <c r="C15" s="102" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="40"/>
-      <c r="E15" s="91" t="s">
+      <c r="E15" s="92" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="40"/>
-      <c r="G15" s="91" t="s">
+      <c r="G15" s="92" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="40"/>
-      <c r="J15" s="91" t="s">
+      <c r="J15" s="92" t="s">
         <v>49</v>
       </c>
       <c r="K15" s="40"/>
-      <c r="L15" s="91" t="s">
+      <c r="L15" s="92" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="39"/>
       <c r="N15" s="40"/>
-      <c r="O15" s="91" t="s">
+      <c r="O15" s="92" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="39"/>
@@ -8862,24 +8863,24 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="93">
+      <c r="A16" s="100">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="101" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="94" t="s">
+      <c r="E16" s="101" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="99" t="s">
+      <c r="G16" s="95" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="99" t="s">
+      <c r="J16" s="95" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="40"/>
@@ -8904,24 +8905,24 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="93">
+      <c r="A17" s="100">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="101" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="94" t="s">
+      <c r="E17" s="101" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="99" t="s">
+      <c r="G17" s="95" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="99" t="s">
+      <c r="J17" s="95" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="40"/>
@@ -8946,16 +8947,16 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="93"/>
+      <c r="A18" s="100"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="94"/>
+      <c r="C18" s="101"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="94"/>
+      <c r="E18" s="101"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="99"/>
+      <c r="G18" s="95"/>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="99"/>
+      <c r="J18" s="95"/>
       <c r="K18" s="40"/>
       <c r="L18" s="97"/>
       <c r="M18" s="39"/>
@@ -8974,16 +8975,16 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="93"/>
+      <c r="A19" s="100"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="94"/>
+      <c r="C19" s="101"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="94"/>
+      <c r="E19" s="101"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="99"/>
+      <c r="G19" s="95"/>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="99"/>
+      <c r="J19" s="95"/>
       <c r="K19" s="40"/>
       <c r="L19" s="97"/>
       <c r="M19" s="39"/>
@@ -9002,16 +9003,16 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="93"/>
+      <c r="A20" s="100"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="94"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="94"/>
+      <c r="E20" s="101"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="99"/>
+      <c r="G20" s="95"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="99"/>
+      <c r="J20" s="95"/>
       <c r="K20" s="40"/>
       <c r="L20" s="97"/>
       <c r="M20" s="39"/>
@@ -9030,16 +9031,16 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="93"/>
+      <c r="A21" s="100"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="94"/>
+      <c r="C21" s="101"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="94"/>
+      <c r="E21" s="101"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="99"/>
+      <c r="G21" s="95"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="99"/>
+      <c r="J21" s="95"/>
       <c r="K21" s="40"/>
       <c r="L21" s="97"/>
       <c r="M21" s="39"/>
@@ -9058,16 +9059,16 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="93"/>
+      <c r="A22" s="100"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="94"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="94"/>
+      <c r="E22" s="101"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="99"/>
+      <c r="G22" s="95"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="99"/>
+      <c r="J22" s="95"/>
       <c r="K22" s="40"/>
       <c r="L22" s="97"/>
       <c r="M22" s="39"/>
@@ -9086,16 +9087,16 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="93"/>
+      <c r="A23" s="100"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="94"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="94"/>
+      <c r="E23" s="101"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="99"/>
+      <c r="G23" s="95"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="99"/>
+      <c r="J23" s="95"/>
       <c r="K23" s="40"/>
       <c r="L23" s="97"/>
       <c r="M23" s="39"/>
@@ -9114,16 +9115,16 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="93"/>
+      <c r="A24" s="100"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="94"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="94"/>
+      <c r="E24" s="101"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="99"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="99"/>
+      <c r="J24" s="95"/>
       <c r="K24" s="40"/>
       <c r="L24" s="97"/>
       <c r="M24" s="39"/>
@@ -9142,16 +9143,16 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="93"/>
+      <c r="A25" s="100"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="94"/>
+      <c r="C25" s="101"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="94"/>
+      <c r="E25" s="101"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="99"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="99"/>
+      <c r="J25" s="95"/>
       <c r="K25" s="40"/>
       <c r="L25" s="97"/>
       <c r="M25" s="39"/>
@@ -9170,16 +9171,16 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="93"/>
+      <c r="A26" s="100"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="94"/>
+      <c r="C26" s="101"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="94"/>
+      <c r="E26" s="101"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="99"/>
+      <c r="G26" s="95"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="99"/>
+      <c r="J26" s="95"/>
       <c r="K26" s="40"/>
       <c r="L26" s="97"/>
       <c r="M26" s="39"/>
@@ -9198,16 +9199,16 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="93"/>
+      <c r="A27" s="100"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="94"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="94"/>
+      <c r="E27" s="101"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="99"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="99"/>
+      <c r="J27" s="95"/>
       <c r="K27" s="40"/>
       <c r="L27" s="97"/>
       <c r="M27" s="39"/>
@@ -9226,16 +9227,16 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="93"/>
+      <c r="A28" s="100"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="94"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="94"/>
+      <c r="E28" s="101"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="99"/>
+      <c r="G28" s="95"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="99"/>
+      <c r="J28" s="95"/>
       <c r="K28" s="40"/>
       <c r="L28" s="97"/>
       <c r="M28" s="39"/>
@@ -9254,16 +9255,16 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="93"/>
+      <c r="A29" s="100"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="94"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="94"/>
+      <c r="E29" s="101"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="99"/>
+      <c r="G29" s="95"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="99"/>
+      <c r="J29" s="95"/>
       <c r="K29" s="40"/>
       <c r="L29" s="97"/>
       <c r="M29" s="39"/>
@@ -9282,16 +9283,16 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="93"/>
+      <c r="A30" s="100"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="94"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="94"/>
+      <c r="E30" s="101"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="99"/>
+      <c r="G30" s="95"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="99"/>
+      <c r="J30" s="95"/>
       <c r="K30" s="40"/>
       <c r="L30" s="97"/>
       <c r="M30" s="39"/>
@@ -9310,23 +9311,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="95"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="102"/>
-      <c r="K31" s="55"/>
+      <c r="A31" s="103"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="78"/>
       <c r="L31" s="98"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="55"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="78"/>
       <c r="O31" s="98"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="55"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="78"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10324,62 +10325,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10404,62 +10405,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/ユースケース記述new_山形.xlsx
+++ b/Documents/ユースケース記述new_山形.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37587A59-9FB5-4C0D-B604-DE2C691BDCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D6CF52-F302-465C-B55E-2101234866DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -232,40 +232,12 @@
 エラーの原因がユーザ名が未入力である旨通知する</t>
   </si>
   <si>
-    <t>登録された情報でログイン</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>登録されている情報でログインする</t>
     <rPh sb="0" eb="2">
       <t>トウロク</t>
     </rPh>
     <rPh sb="7" eb="9">
       <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>①ログイン画面でID、パスワードを入力する
-②入力が終わったらログインボタンを押下する
-③ログイン失敗画面へ遷移する</t>
-    <rPh sb="39" eb="41">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -285,20 +257,6 @@
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー画面からログアウト</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー画面からログアウトする</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -330,12 +288,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>①ログイン画面でID、パスワードを入力する
-②入力が終わったらログインボタンを押下する
-③メニュー画面へ遷移する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザーIDとパスワードが事前に登録されていること、ログイン画面が表示されていること</t>
     <rPh sb="13" eb="15">
       <t>ジゼン</t>
@@ -352,20 +304,81 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>①メニュー画面でログアウトボタンを押下する
-②ログアウト画面が表示される
-③ログイン画面へ遷移する</t>
+    <t>ログイン</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①ログイン失敗画面へ遷移する</t>
+    <rPh sb="5" eb="7">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト画面からログアウトする</t>
     <rPh sb="5" eb="7">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="17" eb="19">
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①ユーザー：ログイン画面でID、パスワードを入力し、入力が終わったらログインボタンを押下する
+②システム：ログインュー処理をしメニュー画面へ遷移する</t>
+    <rPh sb="59" eb="61">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①ユーザー：ログアウト画面で「はい」ボタンを押下する
+②システム：ログアウト処理をし、ログイン画面に遷移する</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="38" eb="40">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="31" eb="33">
-      <t>ヒョウジ</t>
+    <rPh sb="50" eb="52">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①ユーザー：ログアウト画面で「いいえ」ボタンを押下する
+②システム：メニュー画面に遷移する</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1258,29 +1271,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1297,7 +1328,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1321,64 +1358,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1399,17 +1418,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1417,23 +1436,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2825,19 +2838,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -2849,207 +2862,207 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
+      <c r="A2" s="80"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="56" t="s">
+      <c r="C2" s="65"/>
+      <c r="D2" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="60">
-        <v>45805</v>
-      </c>
-      <c r="I2" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="64"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="63"/>
+      <c r="H2" s="68">
+        <v>45806</v>
+      </c>
+      <c r="I2" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="70"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="81" t="s">
-        <v>68</v>
+      <c r="D6" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="82"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="55" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="81" t="s">
-        <v>76</v>
+      <c r="D7" s="52" t="s">
+        <v>72</v>
       </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="82"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="55" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="81" t="s">
-        <v>80</v>
+      <c r="D8" s="52" t="s">
+        <v>75</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="82"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="59" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="83" t="s">
-        <v>79</v>
+      <c r="D9" s="54" t="s">
+        <v>80</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="82"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="74" t="s">
+      <c r="A10" s="57"/>
+      <c r="B10" s="59" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="81"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="82"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74" t="s">
+      <c r="A11" s="58"/>
+      <c r="B11" s="59" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="83" t="s">
-        <v>69</v>
+      <c r="D11" s="54" t="s">
+        <v>78</v>
       </c>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="82"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="55" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="81" t="s">
-        <v>78</v>
+      <c r="D12" s="52" t="s">
+        <v>74</v>
       </c>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="82"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1" thickBot="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="54" t="s">
+      <c r="B16" s="78"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="54" t="s">
+      <c r="E16" s="61"/>
+      <c r="F16" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="55"/>
+      <c r="G16" s="61"/>
       <c r="H16" s="5" t="s">
         <v>8</v>
       </c>
@@ -3061,122 +3074,122 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="49"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="57"/>
-      <c r="F17" s="56" t="s">
+      <c r="C17" s="65"/>
+      <c r="D17" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="57"/>
-      <c r="H17" s="60">
-        <v>45805</v>
-      </c>
-      <c r="I17" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="J17" s="64"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="63"/>
+      <c r="H17" s="68">
+        <v>45806</v>
+      </c>
+      <c r="I17" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="72"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="49"/>
+      <c r="A18" s="80"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="73"/>
     </row>
     <row r="19" spans="1:10" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A19" s="51"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="66"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="74"/>
     </row>
     <row r="20" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="70"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="81" t="s">
-        <v>74</v>
+      <c r="D21" s="52" t="s">
+        <v>79</v>
       </c>
       <c r="E21" s="39"/>
       <c r="F21" s="39"/>
       <c r="G21" s="39"/>
       <c r="H21" s="39"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="82"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="55" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="81" t="s">
-        <v>76</v>
+      <c r="D22" s="52" t="s">
+        <v>72</v>
       </c>
       <c r="E22" s="39"/>
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="82"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="55" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
-      <c r="D23" s="81" t="s">
-        <v>75</v>
+      <c r="D23" s="52" t="s">
+        <v>71</v>
       </c>
       <c r="E23" s="39"/>
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
       <c r="H23" s="39"/>
       <c r="I23" s="39"/>
-      <c r="J23" s="82"/>
+      <c r="J23" s="53"/>
     </row>
     <row r="24" spans="1:10" ht="60" customHeight="1">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="59" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="40"/>
-      <c r="D24" s="83" t="s">
+      <c r="D24" s="54" t="s">
         <v>81</v>
       </c>
       <c r="E24" s="39"/>
@@ -3184,65 +3197,67 @@
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
-      <c r="J24" s="82"/>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A25" s="72"/>
-      <c r="B25" s="74" t="s">
+      <c r="A25" s="57"/>
+      <c r="B25" s="59" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="40"/>
-      <c r="D25" s="81"/>
+      <c r="D25" s="54" t="s">
+        <v>82</v>
+      </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
-      <c r="J25" s="82"/>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" spans="1:10" ht="60" customHeight="1">
-      <c r="A26" s="73"/>
-      <c r="B26" s="74" t="s">
+      <c r="A26" s="58"/>
+      <c r="B26" s="59" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="40"/>
-      <c r="D26" s="83"/>
+      <c r="D26" s="54"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="39"/>
       <c r="H26" s="39"/>
       <c r="I26" s="39"/>
-      <c r="J26" s="82"/>
+      <c r="J26" s="53"/>
     </row>
     <row r="27" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="55" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="81" t="s">
-        <v>77</v>
+      <c r="D27" s="52" t="s">
+        <v>73</v>
       </c>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="39"/>
       <c r="H27" s="39"/>
       <c r="I27" s="39"/>
-      <c r="J27" s="82"/>
+      <c r="J27" s="53"/>
     </row>
     <row r="28" spans="1:10" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A28" s="76" t="s">
+      <c r="A28" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="80"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="48"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4218,19 +4233,31 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="A16:C19"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E19"/>
+    <mergeCell ref="F17:G19"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D21:J21"/>
     <mergeCell ref="D1:E1"/>
@@ -4247,31 +4274,19 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:J20"/>
-    <mergeCell ref="A16:C19"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E19"/>
-    <mergeCell ref="F17:G19"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4293,16 +4308,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4314,40 +4329,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
+      <c r="A2" s="80"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5706,16 +5721,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5727,40 +5742,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
+      <c r="A2" s="80"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7113,16 +7128,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7134,57 +7149,57 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
+      <c r="A2" s="80"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="73"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="70"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="88" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="39"/>
@@ -7195,22 +7210,22 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="82"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="88"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="90"/>
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="49"/>
+      <c r="A8" s="80"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7219,10 +7234,10 @@
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
-      <c r="J8" s="91"/>
+      <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="49"/>
+      <c r="A9" s="80"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7231,10 +7246,10 @@
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="42"/>
-      <c r="J9" s="91"/>
+      <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="49"/>
+      <c r="A10" s="80"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7243,10 +7258,10 @@
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="42"/>
-      <c r="J10" s="91"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="80"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7255,10 +7270,10 @@
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
-      <c r="J11" s="91"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="49"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7267,10 +7282,10 @@
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
-      <c r="J12" s="91"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="49"/>
+      <c r="A13" s="80"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7279,10 +7294,10 @@
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
       <c r="I13" s="42"/>
-      <c r="J13" s="91"/>
+      <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39"/>
@@ -7293,15 +7308,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="82"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="88" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="81"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
@@ -7312,7 +7327,7 @@
       <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="39"/>
@@ -7329,95 +7344,95 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="92" t="s">
+      <c r="H16" s="94" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="82"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="86"/>
+      <c r="A17" s="85"/>
       <c r="B17" s="39"/>
       <c r="C17" s="40"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="81"/>
+      <c r="H17" s="52"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="82"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="86"/>
+      <c r="A18" s="85"/>
       <c r="B18" s="39"/>
       <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="81"/>
+      <c r="H18" s="52"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="82"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="86"/>
+      <c r="A19" s="85"/>
       <c r="B19" s="39"/>
       <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="81"/>
+      <c r="H19" s="52"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="82"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="86"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="81"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="82"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="86"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="81"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="82"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="86"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="81"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="82"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8398,17 +8413,10 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
@@ -8425,10 +8433,17 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8447,133 +8462,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="54" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="54" t="s">
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="54" t="s">
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="54" t="s">
+      <c r="P1" s="61"/>
+      <c r="Q1" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="55"/>
-      <c r="S1" s="54" t="s">
+      <c r="R1" s="61"/>
+      <c r="S1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="70"/>
+      <c r="T1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
+      <c r="A2" s="80"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="90"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="58"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="64"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="64"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="91"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="99"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="69" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="70"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="51"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="88" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="39"/>
@@ -8581,7 +8596,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="81" t="s">
+      <c r="G6" s="52" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -8596,10 +8611,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="82"/>
+      <c r="T6" s="53"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="88" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="39"/>
@@ -8607,7 +8622,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="81" t="s">
+      <c r="G7" s="52" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="39"/>
@@ -8622,7 +8637,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="82"/>
+      <c r="T7" s="53"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8821,7 +8836,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="88" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="40"/>
@@ -8829,25 +8844,25 @@
         <v>40</v>
       </c>
       <c r="D15" s="40"/>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="94" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="40"/>
-      <c r="G15" s="92" t="s">
+      <c r="G15" s="94" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="40"/>
-      <c r="J15" s="92" t="s">
+      <c r="J15" s="94" t="s">
         <v>49</v>
       </c>
       <c r="K15" s="40"/>
-      <c r="L15" s="92" t="s">
+      <c r="L15" s="94" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="39"/>
       <c r="N15" s="40"/>
-      <c r="O15" s="92" t="s">
+      <c r="O15" s="94" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="39"/>
@@ -8863,33 +8878,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="95">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="96" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="101" t="s">
+      <c r="E16" s="96" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="95" t="s">
+      <c r="G16" s="101" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="95" t="s">
+      <c r="J16" s="101" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="40"/>
-      <c r="L16" s="97" t="s">
+      <c r="L16" s="99" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="97" t="s">
+      <c r="O16" s="99" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="39"/>
@@ -8905,33 +8920,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="95">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="96" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="101" t="s">
+      <c r="E17" s="96" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="101" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="95" t="s">
+      <c r="J17" s="101" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="40"/>
-      <c r="L17" s="97" t="s">
+      <c r="L17" s="99" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="97" t="s">
+      <c r="O17" s="99" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="39"/>
@@ -8947,21 +8962,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
+      <c r="A18" s="95"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="101"/>
+      <c r="C18" s="96"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="101"/>
+      <c r="E18" s="96"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="95"/>
+      <c r="G18" s="101"/>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="95"/>
+      <c r="J18" s="101"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="97"/>
+      <c r="L18" s="99"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="97"/>
+      <c r="O18" s="99"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -8975,21 +8990,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="101"/>
+      <c r="C19" s="96"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="101"/>
+      <c r="E19" s="96"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="95"/>
+      <c r="G19" s="101"/>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="95"/>
+      <c r="J19" s="101"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="97"/>
+      <c r="L19" s="99"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="97"/>
+      <c r="O19" s="99"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9003,21 +9018,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
+      <c r="A20" s="95"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="101"/>
+      <c r="C20" s="96"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="101"/>
+      <c r="E20" s="96"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="95"/>
+      <c r="G20" s="101"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="95"/>
+      <c r="J20" s="101"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="97"/>
+      <c r="L20" s="99"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="97"/>
+      <c r="O20" s="99"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9031,21 +9046,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="101"/>
+      <c r="C21" s="96"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="101"/>
+      <c r="E21" s="96"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="95"/>
+      <c r="G21" s="101"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="95"/>
+      <c r="J21" s="101"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="97"/>
+      <c r="L21" s="99"/>
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="97"/>
+      <c r="O21" s="99"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
@@ -9059,21 +9074,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
+      <c r="A22" s="95"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="101"/>
+      <c r="C22" s="96"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="101"/>
+      <c r="E22" s="96"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="95"/>
+      <c r="G22" s="101"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="95"/>
+      <c r="J22" s="101"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="97"/>
+      <c r="L22" s="99"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="97"/>
+      <c r="O22" s="99"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9087,21 +9102,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="101"/>
+      <c r="C23" s="96"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="101"/>
+      <c r="E23" s="96"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="95"/>
+      <c r="G23" s="101"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="95"/>
+      <c r="J23" s="101"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="97"/>
+      <c r="L23" s="99"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="97"/>
+      <c r="O23" s="99"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9115,21 +9130,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
+      <c r="A24" s="95"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="101"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="101"/>
+      <c r="E24" s="96"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="95"/>
+      <c r="G24" s="101"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="95"/>
+      <c r="J24" s="101"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="97"/>
+      <c r="L24" s="99"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="97"/>
+      <c r="O24" s="99"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9143,21 +9158,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="101"/>
+      <c r="C25" s="96"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="101"/>
+      <c r="E25" s="96"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="95"/>
+      <c r="G25" s="101"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="95"/>
+      <c r="J25" s="101"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="97"/>
+      <c r="L25" s="99"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="97"/>
+      <c r="O25" s="99"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9171,21 +9186,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="101"/>
+      <c r="C26" s="96"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="101"/>
+      <c r="E26" s="96"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="95"/>
+      <c r="G26" s="101"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="95"/>
+      <c r="J26" s="101"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="97"/>
+      <c r="L26" s="99"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="97"/>
+      <c r="O26" s="99"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9199,21 +9214,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="101"/>
+      <c r="C27" s="96"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="101"/>
+      <c r="E27" s="96"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="95"/>
+      <c r="G27" s="101"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="95"/>
+      <c r="J27" s="101"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="97"/>
+      <c r="L27" s="99"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="97"/>
+      <c r="O27" s="99"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9227,21 +9242,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="101"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="101"/>
+      <c r="E28" s="96"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="95"/>
+      <c r="G28" s="101"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="95"/>
+      <c r="J28" s="101"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="97"/>
+      <c r="L28" s="99"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="97"/>
+      <c r="O28" s="99"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9255,21 +9270,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="101"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="101"/>
+      <c r="E29" s="96"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="95"/>
+      <c r="G29" s="101"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="95"/>
+      <c r="J29" s="101"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="97"/>
+      <c r="L29" s="99"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="97"/>
+      <c r="O29" s="99"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9283,21 +9298,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="101"/>
+      <c r="C30" s="96"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="101"/>
+      <c r="E30" s="96"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="95"/>
+      <c r="G30" s="101"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="95"/>
+      <c r="J30" s="101"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="97"/>
+      <c r="L30" s="99"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="97"/>
+      <c r="O30" s="99"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9311,23 +9326,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="103"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="78"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="76"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10325,6 +10340,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10349,118 +10476,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/ユースケース記述new_山形.xlsx
+++ b/Documents/ユースケース記述new_山形.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D6CF52-F302-465C-B55E-2101234866DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8ED3931-2B2B-4D04-9B34-6220FC42E450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -288,22 +288,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザーIDとパスワードが事前に登録されていること、ログイン画面が表示されていること</t>
-    <rPh sb="13" eb="15">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ログイン</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -328,20 +312,6 @@
     <t>ログアウト画面からログアウトする</t>
     <rPh sb="5" eb="7">
       <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>①ユーザー：ログイン画面でID、パスワードを入力し、入力が終わったらログインボタンを押下する
-②システム：ログインュー処理をしメニュー画面へ遷移する</t>
-    <rPh sb="59" eb="61">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -378,6 +348,36 @@
       <t>ガメン</t>
     </rPh>
     <rPh sb="41" eb="43">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザIDとパスワードが事前に登録されていること、ログイン画面が表示されていること</t>
+    <rPh sb="12" eb="14">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①ユーザー：ログイン画面でユーザID、パスワードを入力し、入力が終わったらログインボタンを押下する
+②システム：ログインュー処理をしメニュー画面へ遷移する</t>
+    <rPh sb="62" eb="64">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -2912,7 +2912,7 @@
       <c r="B5" s="50"/>
       <c r="C5" s="61"/>
       <c r="D5" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="50"/>
       <c r="F5" s="50"/>
@@ -2960,7 +2960,7 @@
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
       <c r="D8" s="52" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="C9" s="40"/>
       <c r="D9" s="54" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C11" s="40"/>
       <c r="D11" s="54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
@@ -3124,7 +3124,7 @@
       <c r="B20" s="50"/>
       <c r="C20" s="61"/>
       <c r="D20" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" s="50"/>
       <c r="F20" s="50"/>
@@ -3140,7 +3140,7 @@
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="39"/>
       <c r="F21" s="39"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>

--- a/Documents/ユースケース記述new_山形.xlsx
+++ b/Documents/ユースケース記述new_山形.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8ED3931-2B2B-4D04-9B34-6220FC42E450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497850F3-B704-4B04-A5ED-5DE5FE205060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -268,16 +268,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログイン画面が表示される</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>メニュー画面が表示される</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -379,6 +369,39 @@
     </rPh>
     <rPh sb="73" eb="75">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面が遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①ユーザー：ログインしていない状態で画面を開く
+②システム：「ログインされていません」というメッセージと、ログイン画面に誘導するリンクが表示される</t>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1271,72 +1294,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1358,10 +1315,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1376,19 +1342,73 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1398,6 +1418,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1418,17 +1441,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1436,17 +1453,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2838,19 +2861,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="60" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -2862,72 +2885,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
+      <c r="A2" s="61"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62" t="s">
+      <c r="C2" s="62"/>
+      <c r="D2" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="68">
+      <c r="G2" s="68"/>
+      <c r="H2" s="46">
         <v>45806</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="72"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="73"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="71" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="80" t="s">
         <v>67</v>
       </c>
       <c r="E6" s="39"/>
@@ -2935,15 +2958,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="71" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="80" t="s">
         <v>72</v>
       </c>
       <c r="E7" s="39"/>
@@ -2951,118 +2974,118 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="79"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="71" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
-        <v>81</v>
+      <c r="D8" s="80" t="s">
+        <v>80</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="77" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="54" t="s">
-        <v>82</v>
+      <c r="D9" s="78" t="s">
+        <v>81</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="59" t="s">
+      <c r="A10" s="82"/>
+      <c r="B10" s="77" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="52"/>
+      <c r="D10" s="80"/>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="58"/>
-      <c r="B11" s="59" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="77" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="54" t="s">
-        <v>77</v>
+      <c r="D11" s="78" t="s">
+        <v>76</v>
       </c>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="71" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="52" t="s">
-        <v>74</v>
+      <c r="D12" s="80" t="s">
+        <v>73</v>
       </c>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1" thickBot="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="60" t="s">
+      <c r="B16" s="59"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="61"/>
-      <c r="F16" s="60" t="s">
+      <c r="E16" s="55"/>
+      <c r="F16" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="61"/>
+      <c r="G16" s="55"/>
       <c r="H16" s="5" t="s">
         <v>8</v>
       </c>
@@ -3074,88 +3097,88 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="80"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="62" t="s">
+      <c r="C17" s="62"/>
+      <c r="D17" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="63"/>
-      <c r="F17" s="62" t="s">
+      <c r="E17" s="68"/>
+      <c r="F17" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="63"/>
-      <c r="H17" s="68">
+      <c r="G17" s="68"/>
+      <c r="H17" s="46">
         <v>45806</v>
       </c>
-      <c r="I17" s="71" t="s">
+      <c r="I17" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="72"/>
+      <c r="J17" s="50"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="80"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="73"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="51"/>
     </row>
     <row r="19" spans="1:10" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A19" s="81"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="74"/>
+      <c r="A19" s="63"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="52"/>
     </row>
     <row r="20" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="51"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="71" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="52" t="s">
-        <v>78</v>
+      <c r="D21" s="80" t="s">
+        <v>77</v>
       </c>
       <c r="E21" s="39"/>
       <c r="F21" s="39"/>
       <c r="G21" s="39"/>
       <c r="H21" s="39"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="79"/>
     </row>
     <row r="22" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="71" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="80" t="s">
         <v>72</v>
       </c>
       <c r="E22" s="39"/>
@@ -3163,15 +3186,15 @@
       <c r="G22" s="39"/>
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="71" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="80" t="s">
         <v>71</v>
       </c>
       <c r="E23" s="39"/>
@@ -3179,85 +3202,87 @@
       <c r="G23" s="39"/>
       <c r="H23" s="39"/>
       <c r="I23" s="39"/>
-      <c r="J23" s="53"/>
+      <c r="J23" s="79"/>
     </row>
     <row r="24" spans="1:10" ht="60" customHeight="1">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="77" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="40"/>
-      <c r="D24" s="54" t="s">
-        <v>79</v>
+      <c r="D24" s="78" t="s">
+        <v>78</v>
       </c>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
-      <c r="J24" s="53"/>
+      <c r="J24" s="79"/>
     </row>
     <row r="25" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A25" s="57"/>
-      <c r="B25" s="59" t="s">
+      <c r="A25" s="82"/>
+      <c r="B25" s="77" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="40"/>
-      <c r="D25" s="54" t="s">
-        <v>80</v>
+      <c r="D25" s="78" t="s">
+        <v>79</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
-      <c r="J25" s="53"/>
+      <c r="J25" s="79"/>
     </row>
     <row r="26" spans="1:10" ht="60" customHeight="1">
-      <c r="A26" s="58"/>
-      <c r="B26" s="59" t="s">
+      <c r="A26" s="83"/>
+      <c r="B26" s="77" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="40"/>
-      <c r="D26" s="54"/>
+      <c r="D26" s="78" t="s">
+        <v>83</v>
+      </c>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="39"/>
       <c r="H26" s="39"/>
       <c r="I26" s="39"/>
-      <c r="J26" s="53"/>
+      <c r="J26" s="79"/>
     </row>
     <row r="27" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="71" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="52" t="s">
-        <v>73</v>
+      <c r="D27" s="80" t="s">
+        <v>82</v>
       </c>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="39"/>
       <c r="H27" s="39"/>
       <c r="I27" s="39"/>
-      <c r="J27" s="53"/>
+      <c r="J27" s="79"/>
     </row>
     <row r="28" spans="1:10" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A28" s="75" t="s">
+      <c r="A28" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="48"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="76"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4233,31 +4258,19 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:J20"/>
-    <mergeCell ref="A16:C19"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E19"/>
-    <mergeCell ref="F17:G19"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D21:J21"/>
     <mergeCell ref="D1:E1"/>
@@ -4274,19 +4287,31 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="A16:C19"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E19"/>
+    <mergeCell ref="F17:G19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4308,16 +4333,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="60" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4329,40 +4354,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
+      <c r="A2" s="61"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="73"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5721,16 +5746,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="60" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5742,40 +5767,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
+      <c r="A2" s="61"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="73"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7128,16 +7153,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="60" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7149,57 +7174,57 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
+      <c r="A2" s="61"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="73"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="80"/>
+      <c r="A4" s="61"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="73"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="61"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
       <c r="D5" s="89"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="87" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="39"/>
@@ -7210,7 +7235,7 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="90"/>
@@ -7225,7 +7250,7 @@
       <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="80"/>
+      <c r="A8" s="61"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7237,7 +7262,7 @@
       <c r="J8" s="93"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="80"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7249,7 +7274,7 @@
       <c r="J9" s="93"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="80"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7261,7 +7286,7 @@
       <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="80"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7273,7 +7298,7 @@
       <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="80"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7285,7 +7310,7 @@
       <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="80"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7297,7 +7322,7 @@
       <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="87" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39"/>
@@ -7308,15 +7333,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="52"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
@@ -7327,7 +7352,7 @@
       <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="87" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="39"/>
@@ -7348,91 +7373,91 @@
         <v>20</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="53"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="85"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="39"/>
       <c r="C17" s="40"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="52"/>
+      <c r="H17" s="80"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="79"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="85"/>
+      <c r="A18" s="88"/>
       <c r="B18" s="39"/>
       <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="52"/>
+      <c r="H18" s="80"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="53"/>
+      <c r="J18" s="79"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="85"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="39"/>
       <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="52"/>
+      <c r="H19" s="80"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="53"/>
+      <c r="J19" s="79"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="85"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="52"/>
+      <c r="H20" s="80"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="53"/>
+      <c r="J20" s="79"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="52"/>
+      <c r="H21" s="80"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="79"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
+      <c r="H22" s="80"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="76"/>
+      <c r="A23" s="86"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="48"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8413,11 +8438,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8434,16 +8464,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8462,133 +8487,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="60" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="60" t="s">
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="60" t="s">
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="60" t="s">
+      <c r="P1" s="55"/>
+      <c r="Q1" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="61"/>
-      <c r="S1" s="60" t="s">
+      <c r="R1" s="55"/>
+      <c r="S1" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="51"/>
+      <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="80"/>
+      <c r="A2" s="61"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="67"/>
       <c r="H2" s="91"/>
       <c r="I2" s="91"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="62"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="67"/>
       <c r="L2" s="91"/>
       <c r="M2" s="91"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="62"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="67"/>
       <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="80"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="64"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="69"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="64"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="69"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="64"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="69"/>
       <c r="T3" s="93"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="103"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="49" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="51"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="87" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="39"/>
@@ -8596,7 +8621,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="80" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="39"/>
@@ -8611,10 +8636,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="53"/>
+      <c r="T6" s="79"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="87" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="39"/>
@@ -8622,7 +8647,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="80" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="39"/>
@@ -8637,7 +8662,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="53"/>
+      <c r="T7" s="79"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8836,7 +8861,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="87" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="40"/>
@@ -8878,33 +8903,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="95">
+      <c r="A16" s="100">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="101" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="96" t="s">
+      <c r="E16" s="101" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="101" t="s">
+      <c r="G16" s="95" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="101" t="s">
+      <c r="J16" s="95" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="40"/>
-      <c r="L16" s="99" t="s">
+      <c r="L16" s="97" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="99" t="s">
+      <c r="O16" s="97" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="39"/>
@@ -8920,33 +8945,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="100">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="101" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="101" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="101" t="s">
+      <c r="G17" s="95" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="101" t="s">
+      <c r="J17" s="95" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="40"/>
-      <c r="L17" s="99" t="s">
+      <c r="L17" s="97" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="99" t="s">
+      <c r="O17" s="97" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="39"/>
@@ -8962,21 +8987,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="95"/>
+      <c r="A18" s="100"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="96"/>
+      <c r="C18" s="101"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="96"/>
+      <c r="E18" s="101"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="101"/>
+      <c r="G18" s="95"/>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="101"/>
+      <c r="J18" s="95"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="99"/>
+      <c r="L18" s="97"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="99"/>
+      <c r="O18" s="97"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -8990,21 +9015,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="95"/>
+      <c r="A19" s="100"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="96"/>
+      <c r="C19" s="101"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="96"/>
+      <c r="E19" s="101"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="101"/>
+      <c r="G19" s="95"/>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="101"/>
+      <c r="J19" s="95"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="99"/>
+      <c r="L19" s="97"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="99"/>
+      <c r="O19" s="97"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9018,21 +9043,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="95"/>
+      <c r="A20" s="100"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="96"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="96"/>
+      <c r="E20" s="101"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="101"/>
+      <c r="G20" s="95"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="101"/>
+      <c r="J20" s="95"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="99"/>
+      <c r="L20" s="97"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="99"/>
+      <c r="O20" s="97"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9046,21 +9071,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="95"/>
+      <c r="A21" s="100"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="96"/>
+      <c r="C21" s="101"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="96"/>
+      <c r="E21" s="101"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="101"/>
+      <c r="G21" s="95"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="101"/>
+      <c r="J21" s="95"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="99"/>
+      <c r="L21" s="97"/>
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="99"/>
+      <c r="O21" s="97"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
@@ -9074,21 +9099,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="95"/>
+      <c r="A22" s="100"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="96"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="96"/>
+      <c r="E22" s="101"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="101"/>
+      <c r="G22" s="95"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="101"/>
+      <c r="J22" s="95"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="99"/>
+      <c r="L22" s="97"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="99"/>
+      <c r="O22" s="97"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9102,21 +9127,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="95"/>
+      <c r="A23" s="100"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="96"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="96"/>
+      <c r="E23" s="101"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="101"/>
+      <c r="G23" s="95"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="101"/>
+      <c r="J23" s="95"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="99"/>
+      <c r="L23" s="97"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="99"/>
+      <c r="O23" s="97"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9130,21 +9155,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="95"/>
+      <c r="A24" s="100"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="96"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="96"/>
+      <c r="E24" s="101"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="101"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="101"/>
+      <c r="J24" s="95"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="99"/>
+      <c r="L24" s="97"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="99"/>
+      <c r="O24" s="97"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9158,21 +9183,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="95"/>
+      <c r="A25" s="100"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="96"/>
+      <c r="C25" s="101"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="96"/>
+      <c r="E25" s="101"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="101"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="101"/>
+      <c r="J25" s="95"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="99"/>
+      <c r="L25" s="97"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="99"/>
+      <c r="O25" s="97"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9186,21 +9211,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="95"/>
+      <c r="A26" s="100"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="96"/>
+      <c r="C26" s="101"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="96"/>
+      <c r="E26" s="101"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="101"/>
+      <c r="G26" s="95"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="101"/>
+      <c r="J26" s="95"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="99"/>
+      <c r="L26" s="97"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="99"/>
+      <c r="O26" s="97"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9214,21 +9239,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="95"/>
+      <c r="A27" s="100"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="96"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="96"/>
+      <c r="E27" s="101"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="101"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="101"/>
+      <c r="J27" s="95"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="99"/>
+      <c r="L27" s="97"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="99"/>
+      <c r="O27" s="97"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9242,21 +9267,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="95"/>
+      <c r="A28" s="100"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="96"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="96"/>
+      <c r="E28" s="101"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="101"/>
+      <c r="G28" s="95"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="101"/>
+      <c r="J28" s="95"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="99"/>
+      <c r="L28" s="97"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="99"/>
+      <c r="O28" s="97"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9270,21 +9295,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="95"/>
+      <c r="A29" s="100"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="96"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="96"/>
+      <c r="E29" s="101"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="101"/>
+      <c r="G29" s="95"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="101"/>
+      <c r="J29" s="95"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="99"/>
+      <c r="L29" s="97"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="99"/>
+      <c r="O29" s="97"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9298,21 +9323,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="95"/>
+      <c r="A30" s="100"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="96"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="96"/>
+      <c r="E30" s="101"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="101"/>
+      <c r="G30" s="95"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="101"/>
+      <c r="J30" s="95"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="99"/>
+      <c r="L30" s="97"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="99"/>
+      <c r="O30" s="97"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9326,23 +9351,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="76"/>
+      <c r="A31" s="103"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="74"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10340,62 +10365,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10420,62 +10445,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
